--- a/samples/invoices.xlsx
+++ b/samples/invoices.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,9 +410,6 @@
         <v>amount</v>
       </c>
       <c r="D1" t="str">
-        <v>type</v>
-      </c>
-      <c r="E1" t="str">
         <v>reference</v>
       </c>
     </row>
@@ -427,9 +424,6 @@
         <v>1450.00</v>
       </c>
       <c r="D2" t="str">
-        <v>invoice</v>
-      </c>
-      <c r="E2" t="str">
         <v>INV-4021</v>
       </c>
     </row>
@@ -444,9 +438,6 @@
         <v>880.50</v>
       </c>
       <c r="D3" t="str">
-        <v>invoice</v>
-      </c>
-      <c r="E3" t="str">
         <v>INV-4022</v>
       </c>
     </row>
@@ -461,15 +452,12 @@
         <v>312.75</v>
       </c>
       <c r="D4" t="str">
-        <v>invoice</v>
-      </c>
-      <c r="E4" t="str">
         <v>INV-4023</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>